--- a/5/search/FY3_Missile1_results/fine_tuned/original_top5_solutions.xlsx
+++ b/5/search/FY3_Missile1_results/fine_tuned/original_top5_solutions.xlsx
@@ -487,34 +487,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90</v>
+        <v>76.5</v>
       </c>
       <c r="B2" t="n">
-        <v>128.8</v>
+        <v>112</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>6000</v>
+        <v>6732.084661052119</v>
       </c>
       <c r="F2" t="n">
-        <v>-424</v>
+        <v>49.35207036711381</v>
       </c>
       <c r="G2" t="n">
         <v>700</v>
       </c>
       <c r="H2" t="n">
-        <v>6000</v>
+        <v>6732.084661052119</v>
       </c>
       <c r="I2" t="n">
-        <v>91.20000000000005</v>
+        <v>49.35207036711381</v>
       </c>
       <c r="J2" t="n">
-        <v>621.6</v>
+        <v>700</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -522,34 +522,34 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>90</v>
+        <v>76.5</v>
       </c>
       <c r="B3" t="n">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="C3" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>6000</v>
+        <v>6683.528025370091</v>
       </c>
       <c r="F3" t="n">
-        <v>-312</v>
+        <v>-152.9008730756032</v>
       </c>
       <c r="G3" t="n">
         <v>700</v>
       </c>
       <c r="H3" t="n">
-        <v>6000</v>
+        <v>6740.488694150932</v>
       </c>
       <c r="I3" t="n">
-        <v>24</v>
+        <v>84.35738750142991</v>
       </c>
       <c r="J3" t="n">
-        <v>621.6</v>
+        <v>680.4</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -557,37 +557,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>81</v>
+        <v>76.5</v>
       </c>
       <c r="B4" t="n">
-        <v>78.40000000000001</v>
+        <v>132</v>
       </c>
       <c r="C4" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6739.554912695508</v>
+      </c>
+      <c r="F4" t="n">
+        <v>80.46790781983918</v>
+      </c>
+      <c r="G4" t="n">
+        <v>700</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6739.554912695508</v>
+      </c>
+      <c r="I4" t="n">
+        <v>80.46790781983918</v>
+      </c>
+      <c r="J4" t="n">
+        <v>700</v>
+      </c>
+      <c r="K4" t="n">
         <v>3</v>
-      </c>
-      <c r="E4" t="n">
-        <v>6441.520634129548</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-212.3484275042829</v>
-      </c>
-      <c r="G4" t="n">
-        <v>700</v>
-      </c>
-      <c r="H4" t="n">
-        <v>6478.314020307011</v>
-      </c>
-      <c r="I4" t="n">
-        <v>19.95587020369356</v>
-      </c>
-      <c r="J4" t="n">
-        <v>655.9</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -595,69 +595,69 @@
         <v>81</v>
       </c>
       <c r="B5" t="n">
-        <v>89.59999999999999</v>
+        <v>128</v>
       </c>
       <c r="C5" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>6448.52889816335</v>
+        <v>6480.566676603589</v>
       </c>
       <c r="F5" t="n">
-        <v>-168.0999898456212</v>
+        <v>34.17858230826323</v>
       </c>
       <c r="G5" t="n">
         <v>700</v>
       </c>
       <c r="H5" t="n">
-        <v>6476.56195429856</v>
+        <v>6480.566676603589</v>
       </c>
       <c r="I5" t="n">
-        <v>8.89376078902751</v>
+        <v>34.17858230826323</v>
       </c>
       <c r="J5" t="n">
-        <v>680.4</v>
+        <v>700</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="B6" t="n">
-        <v>134.4</v>
+        <v>110</v>
       </c>
       <c r="C6" t="n">
         <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>3719.156366604673</v>
+        <v>6000</v>
       </c>
       <c r="F6" t="n">
-        <v>-719.1563666046723</v>
+        <v>-360</v>
       </c>
       <c r="G6" t="n">
         <v>700</v>
       </c>
       <c r="H6" t="n">
-        <v>2863.840004081426</v>
+        <v>6000</v>
       </c>
       <c r="I6" t="n">
-        <v>136.1599959185756</v>
+        <v>80</v>
       </c>
       <c r="J6" t="n">
-        <v>303.1</v>
+        <v>621.6</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
